--- a/Sample_run/1/student/duynthe180374/TC6/GradeDetail.xlsx
+++ b/Sample_run/1/student/duynthe180374/TC6/GradeDetail.xlsx
@@ -1104,7 +1104,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>54180</x:v>
+        <x:v>41684</x:v>
       </x:c>
       <x:c r="Q2" s="0">
         <x:v>4000</x:v>
@@ -1163,7 +1163,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q3" s="0">
-        <x:v>54180</x:v>
+        <x:v>41684</x:v>
       </x:c>
       <x:c r="R3" s="2" t="s">
         <x:v>48</x:v>
@@ -1216,7 +1216,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P4" s="0">
-        <x:v>54180</x:v>
+        <x:v>41684</x:v>
       </x:c>
       <x:c r="Q4" s="0">
         <x:v>4000</x:v>
@@ -1272,7 +1272,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="P5" s="0">
-        <x:v>54180</x:v>
+        <x:v>41684</x:v>
       </x:c>
       <x:c r="Q5" s="0">
         <x:v>4000</x:v>
@@ -1331,7 +1331,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q6" s="0">
-        <x:v>54180</x:v>
+        <x:v>41684</x:v>
       </x:c>
       <x:c r="R6" s="2" t="s">
         <x:v>48</x:v>
@@ -1440,7 +1440,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P8" s="0">
-        <x:v>54180</x:v>
+        <x:v>41684</x:v>
       </x:c>
       <x:c r="Q8" s="0">
         <x:v>4000</x:v>
@@ -1499,7 +1499,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q9" s="0">
-        <x:v>54180</x:v>
+        <x:v>41684</x:v>
       </x:c>
       <x:c r="R9" s="4" t="s">
         <x:v>62</x:v>
@@ -1555,7 +1555,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q10" s="0">
-        <x:v>54180</x:v>
+        <x:v>41684</x:v>
       </x:c>
       <x:c r="R10" s="2" t="s">
         <x:v>48</x:v>
@@ -1608,7 +1608,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P11" s="0">
-        <x:v>54180</x:v>
+        <x:v>41684</x:v>
       </x:c>
       <x:c r="Q11" s="0">
         <x:v>4000</x:v>
@@ -1720,7 +1720,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P13" s="0">
-        <x:v>54294</x:v>
+        <x:v>51032</x:v>
       </x:c>
       <x:c r="Q13" s="0">
         <x:v>4000</x:v>
@@ -1779,7 +1779,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q14" s="0">
-        <x:v>54294</x:v>
+        <x:v>51032</x:v>
       </x:c>
       <x:c r="R14" s="2" t="s">
         <x:v>48</x:v>
@@ -1832,7 +1832,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P15" s="0">
-        <x:v>54294</x:v>
+        <x:v>51032</x:v>
       </x:c>
       <x:c r="Q15" s="0">
         <x:v>4000</x:v>
@@ -1888,7 +1888,7 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="P16" s="0">
-        <x:v>54294</x:v>
+        <x:v>51032</x:v>
       </x:c>
       <x:c r="Q16" s="0">
         <x:v>4000</x:v>
@@ -1947,7 +1947,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q17" s="0">
-        <x:v>54294</x:v>
+        <x:v>51032</x:v>
       </x:c>
       <x:c r="R17" s="2" t="s">
         <x:v>48</x:v>
@@ -2056,7 +2056,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P19" s="0">
-        <x:v>54294</x:v>
+        <x:v>51032</x:v>
       </x:c>
       <x:c r="Q19" s="0">
         <x:v>4000</x:v>
@@ -2115,7 +2115,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q20" s="0">
-        <x:v>54294</x:v>
+        <x:v>51032</x:v>
       </x:c>
       <x:c r="R20" s="4" t="s">
         <x:v>62</x:v>
@@ -2171,7 +2171,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q21" s="0">
-        <x:v>54294</x:v>
+        <x:v>51032</x:v>
       </x:c>
       <x:c r="R21" s="2" t="s">
         <x:v>48</x:v>
@@ -2224,7 +2224,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P22" s="0">
-        <x:v>54294</x:v>
+        <x:v>51032</x:v>
       </x:c>
       <x:c r="Q22" s="0">
         <x:v>4000</x:v>
